--- a/UPSC_MV-08_BM-05_Giam_sat_margin_ngay.xlsx
+++ b/UPSC_MV-08_BM-05_Giam_sat_margin_ngay.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2">
-  <fileVersion appName="Calc" lowestEdited="4"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <fileVersion appName="Calc"/>
   <workbookPr backupFile="false" showObjects="all" date1904="false"/>
   <workbookProtection/>
   <bookViews>
     <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="0"/>
   </bookViews>
   <sheets>
-    <sheet name="Giám sát margin ngày" sheetId="1" state="visible" r:id="rId3"/>
+    <sheet name="BM-05 Giam sat" sheetId="1" state="visible" r:id="rId3"/>
   </sheets>
   <calcPr iterateCount="100" refMode="A1" iterate="false" iterateDelta="0.0001"/>
   <extLst>
@@ -20,27 +20,18 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="25" uniqueCount="23">
-  <si>
-    <t xml:space="preserve">CÔNG TY CỔ PHẦN CHỨNG KHOÁN UP — BM-05</t>
-  </si>
-  <si>
-    <t xml:space="preserve">BÁO CÁO GIÁM SÁT SỬ DỤNG MARGIN HẰNG NGÀY</t>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="14" uniqueCount="14">
+  <si>
+    <t xml:space="preserve">BM-05 · BÁO CÁO GIÁM SÁT MARGIN HẰNG NGÀY</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MV-08 · Dư nợ vs room theo mã/ngành; % tỷ trọng, ngưỡng cảnh báo, call/force, trạng thái. Ô vàng = nhập tay.</t>
   </si>
   <si>
     <t xml:space="preserve">Ngày báo cáo:</t>
   </si>
   <si>
-    <t xml:space="preserve">...... / ...... / ..........</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Người lập:</t>
-  </si>
-  <si>
-    <t xml:space="preserve">............................</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Mã / Nhóm</t>
+    <t xml:space="preserve">Mã / Ngành</t>
   </si>
   <si>
     <t xml:space="preserve">Hạn mức (đồng)</t>
@@ -49,46 +40,28 @@
     <t xml:space="preserve">Dư nợ hiện tại (đồng)</t>
   </si>
   <si>
-    <t xml:space="preserve">% sử dụng</t>
+    <t xml:space="preserve">% Tỷ trọng</t>
   </si>
   <si>
     <t xml:space="preserve">Ngưỡng cảnh báo</t>
   </si>
   <si>
+    <t xml:space="preserve">Call/Force</t>
+  </si>
+  <si>
     <t xml:space="preserve">Trạng thái</t>
   </si>
   <si>
-    <t xml:space="preserve">VNM</t>
-  </si>
-  <si>
-    <t xml:space="preserve">80/90/100%</t>
-  </si>
-  <si>
-    <t xml:space="preserve">VCB</t>
-  </si>
-  <si>
-    <t xml:space="preserve">XYZ</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TỔNG</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Tổng dư nợ margin (đồng)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Tổng hạn mức / Room (đồng)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Vốn chủ sở hữu (VCSH) (đồng)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Tỷ lệ dư nợ / VCSH (≤ 200%)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Số mã chạm ngưỡng (≥ 80%)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Ghi chú: % sử dụng = Dư nợ / Hạn mức. Trạng thái tự động theo ngưỡng 80% / 90% / 100%.</t>
+    <t xml:space="preserve">Mã A</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ngành NH</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Mã C</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ℹ % Tỷ trọng = Dư nợ / Hạn mức. Trạng thái tự tính theo ngưỡng 80 / 90 / 100% room. Cột Call/Force: nhập số KH/dư nợ có nguy cơ.</t>
   </si>
 </sst>
 </file>
@@ -98,9 +71,9 @@
   <numFmts count="3">
     <numFmt numFmtId="164" formatCode="General"/>
     <numFmt numFmtId="165" formatCode="#,##0"/>
-    <numFmt numFmtId="166" formatCode="0.0%"/>
+    <numFmt numFmtId="166" formatCode="0%"/>
   </numFmts>
-  <fonts count="13">
+  <fonts count="9">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -125,16 +98,16 @@
     </font>
     <font>
       <b val="true"/>
-      <sz val="13"/>
-      <color rgb="FF1F3864"/>
+      <sz val="14"/>
+      <color rgb="FF1E3A5F"/>
       <name val="Arial"/>
       <family val="0"/>
       <charset val="1"/>
     </font>
     <font>
-      <b val="true"/>
-      <sz val="11"/>
-      <color rgb="FF2E5496"/>
+      <i val="true"/>
+      <sz val="9"/>
+      <color rgb="FF6B7280"/>
       <name val="Arial"/>
       <family val="0"/>
       <charset val="1"/>
@@ -142,6 +115,13 @@
     <font>
       <b val="true"/>
       <sz val="10"/>
+      <color rgb="FF1E3A5F"/>
+      <name val="Arial"/>
+      <family val="0"/>
+      <charset val="1"/>
+    </font>
+    <font>
+      <sz val="10"/>
       <name val="Arial"/>
       <family val="0"/>
       <charset val="1"/>
@@ -153,44 +133,8 @@
       <family val="0"/>
       <charset val="1"/>
     </font>
-    <font>
-      <b val="true"/>
-      <sz val="9"/>
-      <color rgb="FFFFFFFF"/>
-      <name val="Arial"/>
-      <family val="0"/>
-      <charset val="1"/>
-    </font>
-    <font>
-      <sz val="9"/>
-      <color rgb="FF0000FF"/>
-      <name val="Arial"/>
-      <family val="0"/>
-      <charset val="1"/>
-    </font>
-    <font>
-      <b val="true"/>
-      <sz val="9"/>
-      <name val="Arial"/>
-      <family val="0"/>
-      <charset val="1"/>
-    </font>
-    <font>
-      <sz val="9"/>
-      <name val="Arial"/>
-      <family val="0"/>
-      <charset val="1"/>
-    </font>
-    <font>
-      <i val="true"/>
-      <sz val="9"/>
-      <color rgb="FF808080"/>
-      <name val="Arial"/>
-      <family val="0"/>
-      <charset val="1"/>
-    </font>
   </fonts>
-  <fills count="5">
+  <fills count="4">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -199,20 +143,14 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF1F7A6D"/>
-        <bgColor rgb="FF008080"/>
+        <fgColor rgb="FFFFF7D6"/>
+        <bgColor rgb="FFFFFFFF"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFD9E1F2"/>
-        <bgColor rgb="FFF2F2F2"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
-        <bgColor rgb="FFFFFFFF"/>
+        <fgColor rgb="FFD5E8F0"/>
+        <bgColor rgb="FFCCFFFF"/>
       </patternFill>
     </fill>
   </fills>
@@ -226,16 +164,16 @@
     </border>
     <border diagonalUp="false" diagonalDown="false">
       <left style="thin">
-        <color rgb="FFBFBFBF"/>
+        <color rgb="FFB8C4D0"/>
       </left>
       <right style="thin">
-        <color rgb="FFBFBFBF"/>
+        <color rgb="FFB8C4D0"/>
       </right>
       <top style="thin">
-        <color rgb="FFBFBFBF"/>
+        <color rgb="FFB8C4D0"/>
       </top>
       <bottom style="thin">
-        <color rgb="FFBFBFBF"/>
+        <color rgb="FFB8C4D0"/>
       </bottom>
       <diagonal/>
     </border>
@@ -265,7 +203,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="23">
+  <cellXfs count="12">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -282,79 +220,35 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="8" fillId="2" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="165" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="166" fontId="10" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="11" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="10" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="166" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="10" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="165" fontId="10" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="166" fontId="10" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="false" applyBorder="true" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="6" fillId="4" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="165" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="165" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="166" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="2" borderId="1" xfId="0" applyFont="false" applyBorder="true" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="6" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="7" fillId="2" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="165" fontId="8" fillId="2" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="166" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="166" fontId="8" fillId="2" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="8" fillId="2" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -382,17 +276,17 @@
       <rgbColor rgb="FF000080"/>
       <rgbColor rgb="FF808000"/>
       <rgbColor rgb="FF800080"/>
-      <rgbColor rgb="FF1F7A6D"/>
-      <rgbColor rgb="FFBFBFBF"/>
+      <rgbColor rgb="FF008080"/>
+      <rgbColor rgb="FFB8C4D0"/>
       <rgbColor rgb="FF808080"/>
       <rgbColor rgb="FF9999FF"/>
       <rgbColor rgb="FF993366"/>
-      <rgbColor rgb="FFF2F2F2"/>
-      <rgbColor rgb="FFCCFFFF"/>
+      <rgbColor rgb="FFFFF7D6"/>
+      <rgbColor rgb="FFD5E8F0"/>
       <rgbColor rgb="FF660066"/>
       <rgbColor rgb="FFFF8080"/>
       <rgbColor rgb="FF0066CC"/>
-      <rgbColor rgb="FFD9E1F2"/>
+      <rgbColor rgb="FFCCCCFF"/>
       <rgbColor rgb="FF000080"/>
       <rgbColor rgb="FFFF00FF"/>
       <rgbColor rgb="FFFFFF00"/>
@@ -415,15 +309,15 @@
       <rgbColor rgb="FFFFCC00"/>
       <rgbColor rgb="FFFF9900"/>
       <rgbColor rgb="FFFF6600"/>
-      <rgbColor rgb="FF666699"/>
+      <rgbColor rgb="FF6B7280"/>
       <rgbColor rgb="FF969696"/>
-      <rgbColor rgb="FF1F3864"/>
+      <rgbColor rgb="FF1E3A5F"/>
       <rgbColor rgb="FF339966"/>
       <rgbColor rgb="FF003300"/>
       <rgbColor rgb="FF333300"/>
       <rgbColor rgb="FF993300"/>
       <rgbColor rgb="FF993366"/>
-      <rgbColor rgb="FF2E5496"/>
+      <rgbColor rgb="FF333399"/>
       <rgbColor rgb="FF333333"/>
     </indexedColors>
   </colors>
@@ -438,34 +332,34 @@
         <a:srgbClr val="000000"/>
       </a:dk1>
       <a:lt1>
-        <a:srgbClr val="FFFFFF"/>
+        <a:srgbClr val="ffffff"/>
       </a:lt1>
       <a:dk2>
-        <a:srgbClr val="1F497D"/>
+        <a:srgbClr val="1f497d"/>
       </a:dk2>
       <a:lt2>
-        <a:srgbClr val="EEECE1"/>
+        <a:srgbClr val="eeece1"/>
       </a:lt2>
       <a:accent1>
-        <a:srgbClr val="4F81BD"/>
+        <a:srgbClr val="4f81bd"/>
       </a:accent1>
       <a:accent2>
-        <a:srgbClr val="C0504D"/>
+        <a:srgbClr val="c0504d"/>
       </a:accent2>
       <a:accent3>
-        <a:srgbClr val="9BBB59"/>
+        <a:srgbClr val="9bbb59"/>
       </a:accent3>
       <a:accent4>
-        <a:srgbClr val="8064A2"/>
+        <a:srgbClr val="8064a2"/>
       </a:accent4>
       <a:accent5>
-        <a:srgbClr val="4BACC6"/>
+        <a:srgbClr val="4bacc6"/>
       </a:accent5>
       <a:accent6>
-        <a:srgbClr val="F79646"/>
+        <a:srgbClr val="f79646"/>
       </a:accent6>
       <a:hlink>
-        <a:srgbClr val="0000FF"/>
+        <a:srgbClr val="0000ff"/>
       </a:hlink>
       <a:folHlink>
         <a:srgbClr val="800080"/>
@@ -610,16 +504,16 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:F22"/>
-  <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <dimension ref="A1:G10"/>
+  <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="16"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="2" style="0" width="20"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="11"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="5" style="0" width="14"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="1" style="0" width="16"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="18"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="12"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="5" style="0" width="14"/>
   </cols>
   <sheetData>
-    <row r="1" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="1" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -633,224 +527,103 @@
       <c r="A3" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="C3" s="4" t="s">
+      <c r="B3" s="4"/>
+    </row>
+    <row r="5" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A5" s="5" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="3" t="s">
+      <c r="B5" s="5" t="s">
         <v>4</v>
       </c>
-      <c r="C4" s="4" t="s">
+      <c r="C5" s="5" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="6" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A6" s="5" t="s">
+      <c r="D5" s="5" t="s">
         <v>6</v>
       </c>
-      <c r="B6" s="5" t="s">
+      <c r="E5" s="5" t="s">
         <v>7</v>
       </c>
-      <c r="C6" s="5" t="s">
+      <c r="F5" s="5" t="s">
         <v>8</v>
       </c>
-      <c r="D6" s="5" t="s">
+      <c r="G5" s="5" t="s">
         <v>9</v>
       </c>
-      <c r="E6" s="5" t="s">
+    </row>
+    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A6" s="6" t="s">
         <v>10</v>
       </c>
-      <c r="F6" s="5" t="s">
-        <v>11</v>
+      <c r="B6" s="7" t="n">
+        <v>200000000000</v>
+      </c>
+      <c r="C6" s="7" t="n">
+        <v>150000000000</v>
+      </c>
+      <c r="D6" s="8" t="n">
+        <f aca="false">IF(B6=0,0,C6/B6)</f>
+        <v>0.75</v>
+      </c>
+      <c r="E6" s="9" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="F6" s="10"/>
+      <c r="G6" s="11" t="str">
+        <f aca="false">IF(D6&gt;=1,"Vượt room",IF(D6&gt;=0.9,"Cảnh báo cao",IF(D6&gt;=E6,"Cảnh báo","An toàn")))</f>
+        <v>An toàn</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="6" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B7" s="7" t="n">
-        <v>175000000000</v>
+        <v>500000000000</v>
       </c>
       <c r="C7" s="7" t="n">
-        <v>120000000000</v>
+        <v>470000000000</v>
       </c>
       <c r="D7" s="8" t="n">
         <f aca="false">IF(B7=0,0,C7/B7)</f>
-        <v>0.685714285714286</v>
-      </c>
-      <c r="E7" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="F7" s="10" t="str">
-        <f aca="false">IF(D7&gt;=1,"Vượt room",IF(D7&gt;=0.9,"Cảnh báo cao",IF(D7&gt;=0.8,"Theo dõi","Bình thường")))</f>
-        <v>Bình thường</v>
+        <v>0.94</v>
+      </c>
+      <c r="E7" s="9" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="F7" s="10"/>
+      <c r="G7" s="11" t="str">
+        <f aca="false">IF(D7&gt;=1,"Vượt room",IF(D7&gt;=0.9,"Cảnh báo cao",IF(D7&gt;=E7,"Cảnh báo","An toàn")))</f>
+        <v>Cảnh báo cao</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="6" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B8" s="7" t="n">
-        <v>1237500000000</v>
+        <v>80000000000</v>
       </c>
       <c r="C8" s="7" t="n">
-        <v>900000000000</v>
+        <v>78000000000</v>
       </c>
       <c r="D8" s="8" t="n">
         <f aca="false">IF(B8=0,0,C8/B8)</f>
-        <v>0.727272727272727</v>
-      </c>
-      <c r="E8" s="9" t="s">
+        <v>0.975</v>
+      </c>
+      <c r="E8" s="9" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="F8" s="10"/>
+      <c r="G8" s="11" t="str">
+        <f aca="false">IF(D8&gt;=1,"Vượt room",IF(D8&gt;=0.9,"Cảnh báo cao",IF(D8&gt;=E8,"Cảnh báo","An toàn")))</f>
+        <v>Cảnh báo cao</v>
+      </c>
+    </row>
+    <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A10" s="2" t="s">
         <v>13</v>
-      </c>
-      <c r="F8" s="10" t="str">
-        <f aca="false">IF(D8&gt;=1,"Vượt room",IF(D8&gt;=0.9,"Cảnh báo cao",IF(D8&gt;=0.8,"Theo dõi","Bình thường")))</f>
-        <v>Bình thường</v>
-      </c>
-    </row>
-    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A9" s="6" t="s">
-        <v>15</v>
-      </c>
-      <c r="B9" s="7" t="n">
-        <v>1404000000</v>
-      </c>
-      <c r="C9" s="7" t="n">
-        <v>1350000000</v>
-      </c>
-      <c r="D9" s="8" t="n">
-        <f aca="false">IF(B9=0,0,C9/B9)</f>
-        <v>0.961538461538462</v>
-      </c>
-      <c r="E9" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="F9" s="10" t="str">
-        <f aca="false">IF(D9&gt;=1,"Vượt room",IF(D9&gt;=0.9,"Cảnh báo cao",IF(D9&gt;=0.8,"Theo dõi","Bình thường")))</f>
-        <v>Cảnh báo cao</v>
-      </c>
-    </row>
-    <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A10" s="11"/>
-      <c r="B10" s="11"/>
-      <c r="C10" s="11"/>
-      <c r="D10" s="12" t="str">
-        <f aca="false">IF(OR(B10="",B10=0),"",C10/B10)</f>
-        <v/>
-      </c>
-      <c r="E10" s="11"/>
-      <c r="F10" s="11" t="str">
-        <f aca="false">IF(B10="","",IF(D10&gt;=1,"Vượt room",IF(D10&gt;=0.9,"Cảnh báo cao",IF(D10&gt;=0.8,"Theo dõi","Bình thường"))))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A11" s="11"/>
-      <c r="B11" s="11"/>
-      <c r="C11" s="11"/>
-      <c r="D11" s="12" t="str">
-        <f aca="false">IF(OR(B11="",B11=0),"",C11/B11)</f>
-        <v/>
-      </c>
-      <c r="E11" s="11"/>
-      <c r="F11" s="11" t="str">
-        <f aca="false">IF(B11="","",IF(D11&gt;=1,"Vượt room",IF(D11&gt;=0.9,"Cảnh báo cao",IF(D11&gt;=0.8,"Theo dõi","Bình thường"))))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A12" s="11"/>
-      <c r="B12" s="11"/>
-      <c r="C12" s="11"/>
-      <c r="D12" s="12" t="str">
-        <f aca="false">IF(OR(B12="",B12=0),"",C12/B12)</f>
-        <v/>
-      </c>
-      <c r="E12" s="11"/>
-      <c r="F12" s="11" t="str">
-        <f aca="false">IF(B12="","",IF(D12&gt;=1,"Vượt room",IF(D12&gt;=0.9,"Cảnh báo cao",IF(D12&gt;=0.8,"Theo dõi","Bình thường"))))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A13" s="11"/>
-      <c r="B13" s="11"/>
-      <c r="C13" s="11"/>
-      <c r="D13" s="12" t="str">
-        <f aca="false">IF(OR(B13="",B13=0),"",C13/B13)</f>
-        <v/>
-      </c>
-      <c r="E13" s="11"/>
-      <c r="F13" s="11" t="str">
-        <f aca="false">IF(B13="","",IF(D13&gt;=1,"Vượt room",IF(D13&gt;=0.9,"Cảnh báo cao",IF(D13&gt;=0.8,"Theo dõi","Bình thường"))))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A14" s="13" t="s">
-        <v>16</v>
-      </c>
-      <c r="B14" s="14" t="n">
-        <f aca="false">SUM(B7:B13)</f>
-        <v>1413904000000</v>
-      </c>
-      <c r="C14" s="14" t="n">
-        <f aca="false">SUM(C7:C13)</f>
-        <v>1021350000000</v>
-      </c>
-      <c r="D14" s="15" t="n">
-        <f aca="false">IF(B14=0,0,C14/B14)</f>
-        <v>0.722361631341308</v>
-      </c>
-      <c r="E14" s="16"/>
-      <c r="F14" s="16"/>
-    </row>
-    <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A16" s="17" t="s">
-        <v>17</v>
-      </c>
-      <c r="B16" s="18" t="n">
-        <f aca="false">C14</f>
-        <v>1021350000000</v>
-      </c>
-    </row>
-    <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A17" s="17" t="s">
-        <v>18</v>
-      </c>
-      <c r="B17" s="18" t="n">
-        <f aca="false">B14</f>
-        <v>1413904000000</v>
-      </c>
-    </row>
-    <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A18" s="17" t="s">
-        <v>19</v>
-      </c>
-      <c r="B18" s="19"/>
-    </row>
-    <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A19" s="17" t="s">
-        <v>20</v>
-      </c>
-      <c r="B19" s="20" t="n">
-        <f aca="false">IF(B18=0,0,B16/B18)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A20" s="17" t="s">
-        <v>21</v>
-      </c>
-      <c r="B20" s="21" t="n">
-        <f aca="false">COUNTIF(D7:D13,"&gt;=0.8")</f>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A22" s="22" t="s">
-        <v>22</v>
       </c>
     </row>
   </sheetData>
